--- a/changes/replus-runtime-v5/candidates/RPL_CUT_MALL.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_CUT_MALL.xlsx
@@ -1,36 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_INDEX" sheetId="1" r:id="R47f050e48df04e55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="2" r:id="R602f1159c4ab482f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_入力フロー" sheetId="3" r:id="Rf5ba61e710c74ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_取替方式" sheetId="4" r:id="R30bdcb406ff245a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02A_商品構造" sheetId="5" r:id="R3426a2f2e2494e23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02B_参照商品" sheetId="6" r:id="Rb1bb4faf6a7a44a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02C_供給方式" sheetId="7" r:id="R99fb16b9f23b49c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02D_対応シリーズ" sheetId="8" r:id="R180f00cfaab64606"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_対応窓種" sheetId="9" r:id="R93ba29033bc84af8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_窓種固有仕様" sheetId="10" r:id="R976aab50880e4597"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_サイズルール" sheetId="11" r:id="Rc6047f31330d4f0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05B_カットモール寸法" sheetId="12" r:id="Rcf67420ba47d480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_色" sheetId="13" r:id="R64eda4c668d14afe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_網戸参照" sheetId="14" r:id="R9b6af5f35fad491b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_ガラス参照" sheetId="15" r:id="Re4b784a698774e69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_施工部材" sheetId="16" r:id="Rb954b39d886d436b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09A_OP依存関係" sheetId="17" r:id="R02ae6599d9174148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_適用条件" sheetId="18" r:id="Rd936155967e6457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10B_現調項目" sheetId="19" r:id="R065a2903c2904b7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C_施工スペース" sheetId="20" r:id="R834df4b04e7e4e83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10D_施工条件" sheetId="21" r:id="Rf64eecc8cb7b4da3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_見積入力テスト" sheetId="22" r:id="R900a0c6f54314aa7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_共通参照" sheetId="23" r:id="R0cdc4e1ac40a4988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12A_他取替方式比較" sheetId="24" r:id="Ra8e6bc857eab4813"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_参照整合性監査" sheetId="25" r:id="Rb5053c4293f847ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_Evidence" sheetId="26" r:id="R32f4e83053304f88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_QA" sheetId="27" r:id="R0b86fc4b44da495d"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="00_INDEX" sheetId="1" r:id="R47f050e48df04e55"/>
+    <sheet name="00_README" sheetId="2" r:id="R602f1159c4ab482f"/>
+    <sheet name="01_入力フロー" sheetId="3" r:id="Rf5ba61e710c74ec2"/>
+    <sheet name="02_取替方式" sheetId="4" r:id="R30bdcb406ff245a0"/>
+    <sheet name="02A_商品構造" sheetId="5" r:id="R3426a2f2e2494e23"/>
+    <sheet name="02B_参照商品" sheetId="6" r:id="Rb1bb4faf6a7a44a9"/>
+    <sheet name="02C_供給方式" sheetId="7" r:id="R99fb16b9f23b49c9"/>
+    <sheet name="02D_対応シリーズ" sheetId="8" r:id="R180f00cfaab64606"/>
+    <sheet name="03_対応窓種" sheetId="9" r:id="R93ba29033bc84af8"/>
+    <sheet name="04_窓種固有仕様" sheetId="10" r:id="R976aab50880e4597"/>
+    <sheet name="05_サイズルール" sheetId="11" r:id="Rc6047f31330d4f0b"/>
+    <sheet name="05B_カットモール寸法" sheetId="12" r:id="Rcf67420ba47d480d"/>
+    <sheet name="06_色" sheetId="13" r:id="R64eda4c668d14afe"/>
+    <sheet name="07_網戸参照" sheetId="14" r:id="R9b6af5f35fad491b"/>
+    <sheet name="08_ガラス参照" sheetId="15" r:id="Re4b784a698774e69"/>
+    <sheet name="09_施工部材" sheetId="16" r:id="Rb954b39d886d436b"/>
+    <sheet name="09A_OP依存関係" sheetId="17" r:id="R02ae6599d9174148"/>
+    <sheet name="10_適用条件" sheetId="18" r:id="Rd936155967e6457f"/>
+    <sheet name="10B_現調項目" sheetId="19" r:id="R065a2903c2904b7f"/>
+    <sheet name="10C_施工スペース" sheetId="20" r:id="R834df4b04e7e4e83"/>
+    <sheet name="10D_施工条件" sheetId="21" r:id="Rf64eecc8cb7b4da3"/>
+    <sheet name="11_見積入力テスト" sheetId="22" r:id="R900a0c6f54314aa7"/>
+    <sheet name="12_共通参照" sheetId="23" r:id="R0cdc4e1ac40a4988"/>
+    <sheet name="12A_他取替方式比較" sheetId="24" r:id="Ra8e6bc857eab4813"/>
+    <sheet name="13_参照整合性監査" sheetId="25" r:id="Rb5053c4293f847ac"/>
+    <sheet name="90_Evidence" sheetId="26" r:id="R32f4e83053304f88"/>
+    <sheet name="99_QA" sheetId="27" r:id="R0b86fc4b44da495d"/>
+    <sheet name="14_UI選択契約" sheetId="28" r:id="rIdReplusUiV9"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -421,6 +422,347 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/replus-ui-v9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="22">
+        <v>リプラス住宅用・共通UI選択契約</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="str" s="22">
+        <v>分類</v>
+      </c>
+      <c r="B2" t="str" s="22">
+        <v>対象</v>
+      </c>
+      <c r="C2" t="str" s="22">
+        <v>依存元</v>
+      </c>
+      <c r="D2" t="str" s="22">
+        <v>処理</v>
+      </c>
+      <c r="E2" t="str" s="22">
+        <v>根拠区分</v>
+      </c>
+      <c r="F2" t="str">
+        <v>revision</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str" s="22">
+        <v>色連動</v>
+      </c>
+      <c r="B3" t="str" s="22">
+        <v>cut_mall_color</v>
+      </c>
+      <c r="C3" t="str" s="22">
+        <v>new_sash_exterior_color</v>
+      </c>
+      <c r="D3" t="str" s="22">
+        <v>{"targetField": "cut_mall_color", "parents": ["new_sash_exterior_color"], "cases": [{"when": {"new_sash_exterior_color": "BLACK"}, "value": "T"}, {"when": {"new_sash_exterior_color": "T"}, "value": "T"}, {"when": {"new_sash_exterior_color": "EXT-T"}, "value": "T"}, {"when": {"new_sash_exterior_color": "EXT-LIX-T"}, "value": "T"}, {"when": {"new_sash_exterior_color": "AUTUMN_BROWN"}, "value": "G"}, {"when": {"new_sash_exterior_color": "G"}, "value": "G"}, {"when": {"new_sash_exterior_color": "EXT-G"}, "value": "G"}, {"when": {"new_sash_exterior_color": "EXT-LIX-G"}, "value": "G"}, {"when": {"new_sash_exterior_color": "SHINE_GRAY"}, "value": "K"}, {"when": {"new_sash_exterior_color": "K"}, "value": "K"}, {"when": {"new_sash_exterior_color": "EXT-K"}, "value": "K"}, {"when": {"new_sash_exterior_color": "EXT-LIX-K"}, "value": "K"}, {"when": {"new_sash_exterior_color": "NATURAL_SILVER"}, "value": "D"}, {"when": {"new_sash_exterior_color": "D"}, "value": "D"}, {"when": {"new_sash_exterior_color": "EXT-D"}, "value": "D"}, {"when": {"new_sash_exterior_color": "EXT-LIX-D"}, "value": "D"}, {"when": {"new_sash_exterior_color": "WHITE"}, "value": "W"}, {"when": {"new_sash_exterior_color": "W"}, "value": "W"}, {"when": {"new_sash_exterior_color": "EXT-W"}, "value": "W"}, {"when": {"new_sash_exterior_color": "EXT-LIX-W"}, "value": "W"}], "resolvedMessage": "本体外観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E3" t="str" s="22">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F3" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str" s="22">
+        <v>色連動</v>
+      </c>
+      <c r="B4" t="str" s="22">
+        <v>interior_adjustment_angle_color</v>
+      </c>
+      <c r="C4" t="str" s="22">
+        <v>new_sash_interior_color</v>
+      </c>
+      <c r="D4" t="str" s="22">
+        <v>{"targetField": "interior_adjustment_angle_color", "parents": ["new_sash_interior_color"], "cases": [{"when": {"new_sash_interior_color": "BLACK"}, "value": "T"}, {"when": {"new_sash_interior_color": "M"}, "value": "T"}, {"when": {"new_sash_interior_color": "INT-M"}, "value": "T"}, {"when": {"new_sash_interior_color": "INT-LIX-M"}, "value": "T"}, {"when": {"new_sash_interior_color": "AUTUMN_BROWN"}, "value": "G"}, {"when": {"new_sash_interior_color": "G"}, "value": "G"}, {"when": {"new_sash_interior_color": "INT-G"}, "value": "G"}, {"when": {"new_sash_interior_color": "INT-LIX-G"}, "value": "G"}, {"when": {"new_sash_interior_color": "SHINE_GRAY"}, "value": "K"}, {"when": {"new_sash_interior_color": "K"}, "value": "K"}, {"when": {"new_sash_interior_color": "INT-K"}, "value": "K"}, {"when": {"new_sash_interior_color": "INT-LIX-K"}, "value": "K"}, {"when": {"new_sash_interior_color": "NATURAL_SILVER"}, "value": "D"}, {"when": {"new_sash_interior_color": "D"}, "value": "D"}, {"when": {"new_sash_interior_color": "INT-D"}, "value": "D"}, {"when": {"new_sash_interior_color": "INT-LIX-D"}, "value": "D"}, {"when": {"new_sash_interior_color": "WHITE"}, "value": "W"}, {"when": {"new_sash_interior_color": "W"}, "value": "W"}, {"when": {"new_sash_interior_color": "INT-W"}, "value": "W"}, {"when": {"new_sash_interior_color": "INT-LIX-W"}, "value": "W"}, {"when": {"new_sash_interior_color": "CREA_MOCHA"}, "value": "C"}, {"when": {"new_sash_interior_color": "C"}, "value": "C"}, {"when": {"new_sash_interior_color": "INT-C"}, "value": "C"}, {"when": {"new_sash_interior_color": "INT-LIX-C"}, "value": "C"}, {"when": {"new_sash_interior_color": "CREA_RUSK"}, "value": "B"}, {"when": {"new_sash_interior_color": "B"}, "value": "B"}, {"when": {"new_sash_interior_color": "INT-B"}, "value": "B"}, {"when": {"new_sash_interior_color": "INT-LIX-B"}, "value": "B"}, {"when": {"new_sash_interior_color": "CREA_PALE"}, "value": "P"}, {"when": {"new_sash_interior_color": "P"}, "value": "P"}, {"when": {"new_sash_interior_color": "INT-P"}, "value": "P"}, {"when": {"new_sash_interior_color": "INT-LIX-P"}, "value": "P"}, {"when": {"new_sash_interior_color": "PRECIOUS_WHITE"}, "value": "F"}, {"when": {"new_sash_interior_color": "F"}, "value": "F"}, {"when": {"new_sash_interior_color": "INT-F"}, "value": "F"}, {"when": {"new_sash_interior_color": "INT-LIX-F"}, "value": "F"}], "resolvedMessage": "本体内観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E4" t="str" s="22">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F4" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B5" t="str" s="22">
+        <v>referenced_series_id</v>
+      </c>
+      <c r="C5" t="str" s="22"/>
+      <c r="D5" t="str" s="22">
+        <v>{"label": "新設サッシシリーズ", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E5" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F5" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B6" t="str" s="22">
+        <v>referenced_window_id</v>
+      </c>
+      <c r="C6" t="str" s="22">
+        <v>referenced_series_id</v>
+      </c>
+      <c r="D6" t="str" s="22">
+        <v>{"label": "新設サッシ窓種", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E6" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F6" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B7" t="str" s="22">
+        <v>cut_mall_color</v>
+      </c>
+      <c r="C7" t="str" s="22">
+        <v>new_sash_exterior_color</v>
+      </c>
+      <c r="D7" t="str" s="22">
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E7" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F7" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B8" t="str" s="22">
+        <v>new_construction_window_frame_color</v>
+      </c>
+      <c r="C8" t="str" s="22"/>
+      <c r="D8" t="str" s="22">
+        <v>{"label": "新設サッシ用窓枠色", "group": "part_detail", "internal": false}</v>
+      </c>
+      <c r="E8" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F8" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B9" t="str" s="22">
+        <v>interior_adjustment_angle_color</v>
+      </c>
+      <c r="C9" t="str" s="22">
+        <v>new_sash_interior_color</v>
+      </c>
+      <c r="D9" t="str" s="22">
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E9" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F9" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B10" t="str" s="22">
+        <v>cut_mall_window_frame_color</v>
+      </c>
+      <c r="C10" t="str" s="22"/>
+      <c r="D10" t="str" s="22">
+        <v>{"label": "カットモール用窓枠色", "group": "part_detail", "internal": false}</v>
+      </c>
+      <c r="E10" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F10" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B11" t="str" s="22">
+        <v>building_structure</v>
+      </c>
+      <c r="C11" t="str" s="22"/>
+      <c r="D11" t="str" s="22">
+        <v>{"label": "建物構造", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E11" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F11" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B12" t="str" s="22">
+        <v>existing_sash_mount</v>
+      </c>
+      <c r="C12" t="str" s="22"/>
+      <c r="D12" t="str" s="22">
+        <v>{"label": "既設サッシの取付方式", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E12" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F12" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B13" t="str" s="22">
+        <v>new_sash_size_relation</v>
+      </c>
+      <c r="C13" t="str" s="22"/>
+      <c r="D13" t="str" s="22">
+        <v>{"label": "新設と既設のサイズ関係", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E13" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F13" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B14" t="str" s="22">
+        <v>existing_window_type</v>
+      </c>
+      <c r="C14" t="str" s="22"/>
+      <c r="D14" t="str" s="22">
+        <v>{"label": "既設窓の付属設備", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E14" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F14" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B15" t="str" s="22">
+        <v>new_sash_mount</v>
+      </c>
+      <c r="C15" t="str" s="22">
+        <v>existing_sash_mount</v>
+      </c>
+      <c r="D15" t="str" s="22">
+        <v>{"label": "新設サッシの取付方式", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E15" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F15" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B16" t="str" s="22">
+        <v>rain_pocket</v>
+      </c>
+      <c r="C16" t="str" s="22">
+        <v>existing_window_type</v>
+      </c>
+      <c r="D16" t="str" s="22">
+        <v>{"label": "雨戸の戸袋仕様", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E16" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F16" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B17" t="str" s="22">
+        <v>survey_w</v>
+      </c>
+      <c r="C17" t="str" s="22"/>
+      <c r="D17" t="str" s="22">
+        <v>{"label": "採寸幅 WS（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E17" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F17" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str" s="22">
+        <v>フロー</v>
+      </c>
+      <c r="B18" t="str" s="22">
+        <v>survey_h</v>
+      </c>
+      <c r="C18" t="str" s="22"/>
+      <c r="D18" t="str" s="22">
+        <v>{"label": "採寸高さ HS（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E18" t="str" s="22">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F18" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -16884,218 +17226,356 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="78" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>01_入力フロー｜Runtime selection flow</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="17" t="str">
-        <x:v>order</x:v>
-      </x:c>
-      <x:c r="B2" s="17" t="str">
-        <x:v>field</x:v>
-      </x:c>
-      <x:c r="C2" s="17" t="str">
-        <x:v>表示名</x:v>
-      </x:c>
-      <x:c r="D2" s="17" t="str">
-        <x:v>rule</x:v>
-      </x:c>
-      <x:c r="E2" s="17" t="str">
-        <x:v>mode</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="22" t="str">
-        <x:v>existing_condition</x:v>
-      </x:c>
-      <x:c r="C3" s="22" t="str">
-        <x:v>既設窓/建物条件</x:v>
-      </x:c>
-      <x:c r="D3" s="22" t="str">
-        <x:v>木造・土間・外付・同品種制限を先行判定</x:v>
-      </x:c>
-      <x:c r="E3" s="22" t="str">
-        <x:v>FILTER</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="22" t="str">
-        <x:v>referenced_series</x:v>
-      </x:c>
-      <x:c r="C4" s="22" t="str">
-        <x:v>対応新設シリーズ</x:v>
-      </x:c>
-      <x:c r="D4" s="22" t="str">
-        <x:v>TW / Ⅱ-H / L / A</x:v>
-      </x:c>
-      <x:c r="E4" s="22" t="str">
-        <x:v>SELECT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="22" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="22" t="str">
-        <x:v>referenced_window</x:v>
-      </x:c>
-      <x:c r="C5" s="22" t="str">
-        <x:v>対応窓種</x:v>
-      </x:c>
-      <x:c r="D5" s="22" t="str">
-        <x:v>公式対応×正本active/selectable</x:v>
-      </x:c>
-      <x:c r="E5" s="22" t="str">
-        <x:v>FILTER</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="22" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" s="22" t="str">
-        <x:v>referenced_spec</x:v>
-      </x:c>
-      <x:c r="C6" s="22" t="str">
-        <x:v>固有仕様</x:v>
-      </x:c>
-      <x:c r="D6" s="22" t="str">
-        <x:v>各正本へ委譲</x:v>
-      </x:c>
-      <x:c r="E6" s="22" t="str">
-        <x:v>REFERENCE</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B7" s="22" t="str">
-        <x:v>new_sash_size</x:v>
-      </x:c>
-      <x:c r="C7" s="22" t="str">
-        <x:v>新設サッシW/H</x:v>
-      </x:c>
-      <x:c r="D7" s="22" t="str">
-        <x:v>正本サイズ可否</x:v>
-      </x:c>
-      <x:c r="E7" s="22" t="str">
-        <x:v>REFERENCE</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="22" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B8" s="22" t="str">
-        <x:v>cut_mall_dimension</x:v>
-      </x:c>
-      <x:c r="C8" s="22" t="str">
-        <x:v>MW/MH</x:v>
-      </x:c>
-      <x:c r="D8" s="22" t="str">
-        <x:v>RPL_CUT_MALL公式寸法式</x:v>
-      </x:c>
-      <x:c r="E8" s="22" t="str">
-        <x:v>AUTO</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="22" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" s="22" t="str">
-        <x:v>construction_check</x:v>
-      </x:c>
-      <x:c r="C9" s="22" t="str">
-        <x:v>施工スペース/壁切断/下地</x:v>
-      </x:c>
-      <x:c r="D9" s="22" t="str">
-        <x:v>ローカル判定</x:v>
-      </x:c>
-      <x:c r="E9" s="22" t="str">
-        <x:v>FILTER</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="22" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B10" s="22" t="str">
-        <x:v>body_specs</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="str">
-        <x:v>色→網戸→ガラス→OP</x:v>
-      </x:c>
-      <x:c r="D10" s="22" t="str">
-        <x:v>参照正本から取得</x:v>
-      </x:c>
-      <x:c r="E10" s="22" t="str">
-        <x:v>REFERENCE</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="22" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" s="22" t="str">
-        <x:v>required_parts</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="str">
-        <x:v>施工部材</x:v>
-      </x:c>
-      <x:c r="D11" s="22" t="str">
-        <x:v>条件からAUTO_RESOLVED</x:v>
-      </x:c>
-      <x:c r="E11" s="22" t="str">
-        <x:v>AUTO</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="22" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B12" s="22" t="str">
-        <x:v>final</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="str">
-        <x:v>最終可否</x:v>
-      </x:c>
-      <x:c r="D12" s="22" t="str">
-        <x:v>不成立候補はHIDE/REJECT</x:v>
-      </x:c>
-      <x:c r="E12" s="22" t="str">
-        <x:v>RESOLVE</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="78" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="4">
+        <v>リプラス住宅用・グローバルセレクションフロー</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="str" s="22">
+        <v>順番</v>
+      </c>
+      <c r="B3" t="str" s="22">
+        <v>表示項目</v>
+      </c>
+      <c r="C3" t="str" s="22">
+        <v>データキー</v>
+      </c>
+      <c r="D3" t="str" s="22">
+        <v>候補/入力</v>
+      </c>
+      <c r="E3" t="str" s="22">
+        <v>制御方針</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="22">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str" s="22">
+        <v>商品・リプラス仕様</v>
+      </c>
+      <c r="C4" t="str" s="22">
+        <v>product / specification</v>
+      </c>
+      <c r="D4" t="str" s="22">
+        <v>リプラス住宅用 → 仕様</v>
+      </c>
+      <c r="E4" t="str" s="22">
+        <v>今回承認されたアプリ運用ルール</v>
+      </c>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="22">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str" s="22">
+        <v>設置・施工条件</v>
+      </c>
+      <c r="C5" t="str" s="22">
+        <v>context</v>
+      </c>
+      <c r="D5" t="str" s="22">
+        <v>選択・確認</v>
+      </c>
+      <c r="E5" t="str" s="22">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="22">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str" s="22">
+        <v>窓種・基本仕様</v>
+      </c>
+      <c r="C6" t="str" s="22">
+        <v>opening</v>
+      </c>
+      <c r="D6" t="str" s="22">
+        <v>選択・確認</v>
+      </c>
+      <c r="E6" t="str" s="22">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="22">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str" s="22">
+        <v>本体色</v>
+      </c>
+      <c r="C7" t="str" s="22">
+        <v>finish</v>
+      </c>
+      <c r="D7" t="str" s="22">
+        <v>選択・確認</v>
+      </c>
+      <c r="E7" t="str" s="22">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="22">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str" s="22">
+        <v>網戸</v>
+      </c>
+      <c r="C8" t="str" s="22">
+        <v>screen</v>
+      </c>
+      <c r="D8" t="str" s="22">
+        <v>選択・確認</v>
+      </c>
+      <c r="E8" t="str" s="22">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="22">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str" s="22">
+        <v>ガラス</v>
+      </c>
+      <c r="C9" t="str" s="22">
+        <v>glazing</v>
+      </c>
+      <c r="D9" t="str" s="22">
+        <v>選択・確認</v>
+      </c>
+      <c r="E9" t="str" s="22">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="22">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str" s="22">
+        <v>室内側の仕上げ・アングルカバー</v>
+      </c>
+      <c r="C10" t="str" s="22">
+        <v>interior_finish</v>
+      </c>
+      <c r="D10" t="str" s="22">
+        <v>選択・確認</v>
+      </c>
+      <c r="E10" t="str" s="22">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="22">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str" s="22">
+        <v>室外側の仕上げ・化粧カバー</v>
+      </c>
+      <c r="C11" t="str" s="22">
+        <v>exterior_finish</v>
+      </c>
+      <c r="D11" t="str" s="22">
+        <v>選択・確認</v>
+      </c>
+      <c r="E11" t="str" s="22">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="22">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str" s="22">
+        <v>新設サッシのオプション</v>
+      </c>
+      <c r="C12" t="str" s="22">
+        <v>native_options</v>
+      </c>
+      <c r="D12" t="str" s="22">
+        <v>選択・確認</v>
+      </c>
+      <c r="E12" t="str" s="22">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>追加部材・オプション</v>
+      </c>
+      <c r="C13" t="str">
+        <v>options</v>
+      </c>
+      <c r="D13" t="str">
+        <v>選択・確認</v>
+      </c>
+      <c r="E13" t="str">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>選択した部材の仕様</v>
+      </c>
+      <c r="C14" t="str">
+        <v>part_detail</v>
+      </c>
+      <c r="D14" t="str">
+        <v>選択・確認</v>
+      </c>
+      <c r="E14" t="str">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str">
+        <v>現場採寸・取付条件</v>
+      </c>
+      <c r="C15" t="str">
+        <v>survey</v>
+      </c>
+      <c r="D15" t="str">
+        <v>選択・確認</v>
+      </c>
+      <c r="E15" t="str">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str">
+        <v>製品寸法</v>
+      </c>
+      <c r="C16" t="str">
+        <v>size</v>
+      </c>
+      <c r="D16" t="str">
+        <v>選択・確認</v>
+      </c>
+      <c r="E16" t="str">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+    </row>
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+    </row>
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+    </row>
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+    </row>
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+    </row>
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/changes/replus-runtime-v5/candidates/RPL_CUT_MALL.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_CUT_MALL.xlsx
@@ -473,7 +473,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -531,7 +531,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -551,7 +551,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -569,7 +569,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -589,7 +589,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -607,7 +607,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -619,13 +619,13 @@
       </c>
       <c r="C11" t="str" s="22"/>
       <c r="D11" t="str" s="22">
-        <v>{"label": "建物構造", "group": "context", "internal": false}</v>
+        <v>{"label": "建物構造", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E11" t="str" s="22">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -643,7 +643,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -661,7 +661,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -679,7 +679,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -699,7 +699,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -719,7 +719,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -737,7 +737,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -755,7 +755,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -17331,16 +17331,16 @@
         <v>4</v>
       </c>
       <c r="B7" t="str" s="22">
-        <v>本体色</v>
+        <v>室内側の仕上げ・アングルカバー</v>
       </c>
       <c r="C7" t="str" s="22">
-        <v>finish</v>
+        <v>interior_finish</v>
       </c>
       <c r="D7" t="str" s="22">
         <v>選択・確認</v>
       </c>
       <c r="E7" t="str" s="22">
-        <v>対応する項目のみ表示</v>
+        <v>本体色に連動</v>
       </c>
       <c r="F7"/>
     </row>
@@ -17349,16 +17349,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="str" s="22">
-        <v>網戸</v>
+        <v>室外側の仕上げ・化粧カバー</v>
       </c>
       <c r="C8" t="str" s="22">
-        <v>screen</v>
+        <v>exterior_finish</v>
       </c>
       <c r="D8" t="str" s="22">
         <v>選択・確認</v>
       </c>
       <c r="E8" t="str" s="22">
-        <v>対応する項目のみ表示</v>
+        <v>本体色に連動</v>
       </c>
       <c r="F8"/>
     </row>
@@ -17367,10 +17367,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="str" s="22">
-        <v>ガラス</v>
+        <v>選択した部材の仕様</v>
       </c>
       <c r="C9" t="str" s="22">
-        <v>glazing</v>
+        <v>part_detail</v>
       </c>
       <c r="D9" t="str" s="22">
         <v>選択・確認</v>
@@ -17385,125 +17385,65 @@
         <v>7</v>
       </c>
       <c r="B10" t="str" s="22">
-        <v>室内側の仕上げ・アングルカバー</v>
+        <v>現場採寸・取付条件</v>
       </c>
       <c r="C10" t="str" s="22">
-        <v>interior_finish</v>
+        <v>survey</v>
       </c>
       <c r="D10" t="str" s="22">
         <v>選択・確認</v>
       </c>
       <c r="E10" t="str" s="22">
-        <v>本体色に連動</v>
+        <v>採寸後に再評価</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11">
-      <c r="A11" t="n" s="22">
-        <v>8</v>
-      </c>
-      <c r="B11" t="str" s="22">
-        <v>室外側の仕上げ・化粧カバー</v>
-      </c>
-      <c r="C11" t="str" s="22">
-        <v>exterior_finish</v>
-      </c>
-      <c r="D11" t="str" s="22">
-        <v>選択・確認</v>
-      </c>
-      <c r="E11" t="str" s="22">
-        <v>本体色に連動</v>
-      </c>
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
       <c r="F11"/>
     </row>
     <row r="12">
-      <c r="A12" t="n" s="22">
-        <v>9</v>
-      </c>
-      <c r="B12" t="str" s="22">
-        <v>新設サッシのオプション</v>
-      </c>
-      <c r="C12" t="str" s="22">
-        <v>native_options</v>
-      </c>
-      <c r="D12" t="str" s="22">
-        <v>選択・確認</v>
-      </c>
-      <c r="E12" t="str" s="22">
-        <v>対応する項目のみ表示</v>
-      </c>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
       <c r="F12"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="str">
-        <v>追加部材・オプション</v>
-      </c>
-      <c r="C13" t="str">
-        <v>options</v>
-      </c>
-      <c r="D13" t="str">
-        <v>選択・確認</v>
-      </c>
-      <c r="E13" t="str">
-        <v>対応する項目のみ表示</v>
-      </c>
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
       <c r="F13"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="str">
-        <v>選択した部材の仕様</v>
-      </c>
-      <c r="C14" t="str">
-        <v>part_detail</v>
-      </c>
-      <c r="D14" t="str">
-        <v>選択・確認</v>
-      </c>
-      <c r="E14" t="str">
-        <v>対応する項目のみ表示</v>
-      </c>
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
       <c r="F14"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="str">
-        <v>現場採寸・取付条件</v>
-      </c>
-      <c r="C15" t="str">
-        <v>survey</v>
-      </c>
-      <c r="D15" t="str">
-        <v>選択・確認</v>
-      </c>
-      <c r="E15" t="str">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
       <c r="F15"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="str">
-        <v>製品寸法</v>
-      </c>
-      <c r="C16" t="str">
-        <v>size</v>
-      </c>
-      <c r="D16" t="str">
-        <v>選択・確認</v>
-      </c>
-      <c r="E16" t="str">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
       <c r="F16"/>
     </row>
     <row r="17">

--- a/changes/replus-runtime-v5/candidates/RPL_CUT_MALL.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_CUT_MALL.xlsx
@@ -458,7 +458,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str" s="22">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B3" t="str" s="22">
         <v>cut_mall_color</v>
@@ -473,12 +473,12 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str" s="22">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B4" t="str" s="22">
         <v>interior_adjustment_angle_color</v>
@@ -493,7 +493,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -531,7 +531,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -551,7 +551,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -569,7 +569,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -589,7 +589,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -607,7 +607,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -615,17 +615,17 @@
         <v>フロー</v>
       </c>
       <c r="B11" t="str" s="22">
-        <v>building_structure</v>
+        <v>existing_sash_mount</v>
       </c>
       <c r="C11" t="str" s="22"/>
       <c r="D11" t="str" s="22">
-        <v>{"label": "建物構造", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "既設サッシの取付方式", "group": "context", "internal": false}</v>
       </c>
       <c r="E11" t="str" s="22">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -633,17 +633,17 @@
         <v>フロー</v>
       </c>
       <c r="B12" t="str" s="22">
-        <v>existing_sash_mount</v>
+        <v>new_sash_size_relation</v>
       </c>
       <c r="C12" t="str" s="22"/>
       <c r="D12" t="str" s="22">
-        <v>{"label": "既設サッシの取付方式", "group": "context", "internal": false}</v>
+        <v>{"label": "新設と既設のサイズ関係", "group": "context", "internal": false}</v>
       </c>
       <c r="E12" t="str" s="22">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -651,17 +651,17 @@
         <v>フロー</v>
       </c>
       <c r="B13" t="str" s="22">
-        <v>new_sash_size_relation</v>
+        <v>existing_window_type</v>
       </c>
       <c r="C13" t="str" s="22"/>
       <c r="D13" t="str" s="22">
-        <v>{"label": "新設と既設のサイズ関係", "group": "context", "internal": false}</v>
+        <v>{"label": "既設窓の付属設備", "group": "context", "internal": false}</v>
       </c>
       <c r="E13" t="str" s="22">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -669,17 +669,19 @@
         <v>フロー</v>
       </c>
       <c r="B14" t="str" s="22">
-        <v>existing_window_type</v>
-      </c>
-      <c r="C14" t="str" s="22"/>
+        <v>new_sash_mount</v>
+      </c>
+      <c r="C14" t="str" s="22">
+        <v>existing_sash_mount</v>
+      </c>
       <c r="D14" t="str" s="22">
-        <v>{"label": "既設窓の付属設備", "group": "context", "internal": false}</v>
+        <v>{"label": "新設サッシの取付方式", "group": "context", "internal": false}</v>
       </c>
       <c r="E14" t="str" s="22">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -687,19 +689,19 @@
         <v>フロー</v>
       </c>
       <c r="B15" t="str" s="22">
-        <v>new_sash_mount</v>
+        <v>rain_pocket</v>
       </c>
       <c r="C15" t="str" s="22">
-        <v>existing_sash_mount</v>
+        <v>existing_window_type</v>
       </c>
       <c r="D15" t="str" s="22">
-        <v>{"label": "新設サッシの取付方式", "group": "context", "internal": false}</v>
+        <v>{"label": "雨戸の戸袋仕様", "group": "context", "internal": false}</v>
       </c>
       <c r="E15" t="str" s="22">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -707,19 +709,17 @@
         <v>フロー</v>
       </c>
       <c r="B16" t="str" s="22">
-        <v>rain_pocket</v>
-      </c>
-      <c r="C16" t="str" s="22">
-        <v>existing_window_type</v>
-      </c>
+        <v>survey_w</v>
+      </c>
+      <c r="C16" t="str" s="22"/>
       <c r="D16" t="str" s="22">
-        <v>{"label": "雨戸の戸袋仕様", "group": "context", "internal": false}</v>
+        <v>{"label": "採寸幅 WS（mm）", "group": "survey", "internal": false}</v>
       </c>
       <c r="E16" t="str" s="22">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -727,17 +727,17 @@
         <v>フロー</v>
       </c>
       <c r="B17" t="str" s="22">
-        <v>survey_w</v>
+        <v>survey_h</v>
       </c>
       <c r="C17" t="str" s="22"/>
       <c r="D17" t="str" s="22">
-        <v>{"label": "採寸幅 WS（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "採寸高さ HS（mm）", "group": "survey", "internal": false}</v>
       </c>
       <c r="E17" t="str" s="22">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -13436,7 +13436,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="str">
+      <c r="A1" t="str" s="4">
         <v>90_Evidence｜RPL_CUT_MALL</v>
       </c>
       <c r="B1" s="4"/>
@@ -13449,778 +13449,670 @@
       <c r="I1" s="4"/>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="str">
+      <c r="A2" t="str" s="17">
         <v>evidence_id</v>
       </c>
-      <c r="B2" s="17" t="str">
+      <c r="B2" t="str" s="17">
         <v>source_type</v>
       </c>
-      <c r="C2" s="17" t="str">
+      <c r="C2" t="str" s="17">
         <v>material_title</v>
       </c>
-      <c r="D2" s="17" t="str">
+      <c r="D2" t="str" s="17">
         <v>publication/version</v>
       </c>
-      <c r="E2" s="17" t="str">
+      <c r="E2" t="str" s="17">
         <v>page/sheet</v>
       </c>
-      <c r="F2" s="17" t="str">
+      <c r="F2" t="str" s="17">
         <v>source</v>
       </c>
-      <c r="G2" s="17" t="str">
+      <c r="G2" t="str" s="17">
         <v>checked_at</v>
       </c>
-      <c r="H2" s="17" t="str">
+      <c r="H2" t="str" s="17">
         <v>confidence</v>
       </c>
-      <c r="I2" s="17" t="str">
+      <c r="I2" t="str" s="17">
         <v>summary</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="str">
+      <c r="A3" t="str" s="22">
         <v>CM-EV-001</v>
       </c>
-      <c r="B3" s="22" t="str">
+      <c r="B3" t="str" s="22">
         <v>共通仕様</v>
       </c>
-      <c r="C3" s="22" t="str">
+      <c r="C3" t="str" s="22">
         <v>サッシ商品マスター共通仕様書</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" t="str" s="22">
         <v>current</v>
       </c>
-      <c r="E3" s="22" t="str">
+      <c r="E3" t="str" s="22">
         <v>参照型Master/状態/Dependency/QA</v>
       </c>
-      <c r="F3" s="22" t="str">
+      <c r="F3" t="str" s="22">
         <v>Google Drive</v>
       </c>
-      <c r="G3" s="22" t="str">
+      <c r="G3" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H3" s="22" t="str">
+      <c r="H3" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I3" s="22" t="str">
+      <c r="I3" t="str" s="22">
         <v>共通Master原則</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="str">
+      <c r="A4" t="str" s="22">
         <v>CM-EV-002</v>
       </c>
-      <c r="B4" s="22" t="str">
+      <c r="B4" t="str" s="22">
         <v>LIXIL公式カタログ</v>
       </c>
-      <c r="C4" s="22" t="str">
+      <c r="C4" t="str" s="22">
         <v>リプラス 商品カタログ</v>
       </c>
-      <c r="D4" s="22" t="str">
+      <c r="D4" t="str" s="22">
         <v>2025-08/2026現行</v>
       </c>
-      <c r="E4" s="22" t="str">
+      <c r="E4" t="str" s="22">
         <v>P25/P203/P273等</v>
       </c>
-      <c r="F4" s="22" t="str">
+      <c r="F4" t="str" s="22">
         <v>Drive:1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT</v>
       </c>
-      <c r="G4" s="22" t="str">
+      <c r="G4" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H4" s="22" t="str">
+      <c r="H4" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I4" s="22" t="str">
+      <c r="I4" t="str" s="22">
         <v>汎用カットモールの役割、対応新設商品、同品種制限</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="str">
+      <c r="A5" t="str" s="22">
         <v>CM-EV-003</v>
       </c>
-      <c r="B5" s="22" t="str">
+      <c r="B5" t="str" s="22">
         <v>商品Master正本</v>
       </c>
-      <c r="C5" s="22" t="str">
+      <c r="C5" t="str" s="22">
         <v>サッシ商品マスター_v0.1</v>
       </c>
-      <c r="D5" s="22" t="str">
+      <c r="D5" t="str" s="22">
         <v>integrated-v0.1</v>
       </c>
-      <c r="E5" s="22" t="str">
+      <c r="E5" t="str" s="22">
         <v>03_窓種/03A_シリーズ窓種設定</v>
       </c>
-      <c r="F5" s="22" t="str">
+      <c r="F5" t="str" s="22">
         <v>Drive:1ordbcPQS7XhptLMjRON2oxmdsPhs-aY-Wm7quPHvM9U</v>
       </c>
-      <c r="G5" s="22" t="str">
+      <c r="G5" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H5" s="22" t="str">
+      <c r="H5" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I5" s="22" t="str">
+      <c r="I5" t="str" s="22">
         <v>TW正式ID</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="str">
+      <c r="A6" t="str" s="22">
         <v>CM-EV-004</v>
       </c>
-      <c r="B6" s="22" t="str">
+      <c r="B6" t="str" s="22">
         <v>商品Master正本</v>
       </c>
-      <c r="C6" s="22" t="str">
+      <c r="C6" t="str" s="22">
         <v>サーモスⅡH_商品マスター_v0.7_完全完成版</v>
       </c>
-      <c r="D6" s="22" t="str">
+      <c r="D6" t="str" s="22">
         <v>v0.7</v>
       </c>
-      <c r="E6" s="22" t="str">
+      <c r="E6" t="str" s="22">
         <v>03_窓種/04_窓種固有仕様/06_サイズ</v>
       </c>
-      <c r="F6" s="22" t="str">
+      <c r="F6" t="str" s="22">
         <v>Drive:1zHi-XsMqJp0MKH-sDoTcnTqkLMGcuRdo</v>
       </c>
-      <c r="G6" s="22" t="str">
+      <c r="G6" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H6" s="22" t="str">
+      <c r="H6" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I6" s="22" t="str">
+      <c r="I6" t="str" s="22">
         <v>サーモスⅡ-H SSOT</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="str">
+      <c r="A7" t="str" s="22">
         <v>CM-EV-005</v>
       </c>
-      <c r="B7" s="22" t="str">
+      <c r="B7" t="str" s="22">
         <v>商品Master正本</v>
       </c>
-      <c r="C7" s="22" t="str">
+      <c r="C7" t="str" s="22">
         <v>サーモスL_商品マスター_v0.7_特注寸法発注アプリ投入完成版_QA確定</v>
       </c>
-      <c r="D7" s="22" t="str">
+      <c r="D7" t="str" s="22">
         <v>v0.7</v>
       </c>
-      <c r="E7" s="22" t="str">
+      <c r="E7" t="str" s="22">
         <v>03_窓種/04_窓種固有仕様/06_サイズ</v>
       </c>
-      <c r="F7" s="22" t="str">
+      <c r="F7" t="str" s="22">
         <v>Drive:17lVzBZ1hp4RVcGv0yNdnrKt25SFO2FhL</v>
       </c>
-      <c r="G7" s="22" t="str">
+      <c r="G7" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H7" s="22" t="str">
+      <c r="H7" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I7" s="22" t="str">
+      <c r="I7" t="str" s="22">
         <v>サーモスL SSOT</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="str">
+      <c r="A8" t="str" s="22">
         <v>CM-EV-006</v>
       </c>
-      <c r="B8" s="22" t="str">
+      <c r="B8" t="str" s="22">
         <v>商品Master正本</v>
       </c>
-      <c r="C8" s="22" t="str">
+      <c r="C8" t="str" s="22">
         <v>サーモスA_商品マスター_v0.7</v>
       </c>
-      <c r="D8" s="22" t="str">
+      <c r="D8" t="str" s="22">
         <v>v0.7</v>
       </c>
-      <c r="E8" s="22" t="str">
+      <c r="E8" t="str" s="22">
         <v>02_WINDOW_TYPE_MASTER/12_SIZE_MASTER/15_DEPENDENCY_RULE</v>
       </c>
-      <c r="F8" s="22" t="str">
+      <c r="F8" t="str" s="22">
         <v>Drive:1cDEFzi0g1DzM5YoeGvZtHuXionD7tmFD</v>
       </c>
-      <c r="G8" s="22" t="str">
+      <c r="G8" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H8" s="22" t="str">
+      <c r="H8" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I8" s="22" t="str">
+      <c r="I8" t="str" s="22">
         <v>サーモスA SSOT</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="str">
+      <c r="A9" t="str" s="22">
         <v>CM-EV-007</v>
       </c>
-      <c r="B9" s="22" t="str">
+      <c r="B9" t="str" s="22">
         <v>LIXIL公式納まり</v>
       </c>
-      <c r="C9" s="22" t="str">
+      <c r="C9" t="str" s="22">
         <v>リプラス 汎用カットモール 基本寸法/納まり</v>
       </c>
-      <c r="D9" s="22" t="str">
+      <c r="D9" t="str" s="22">
         <v>2026現行</v>
       </c>
-      <c r="E9" s="22" t="str">
+      <c r="E9" t="str" s="22">
         <v>P189-193</v>
       </c>
-      <c r="F9" s="22" t="str">
+      <c r="F9" t="str" s="22">
         <v>Drive:1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT</v>
       </c>
-      <c r="G9" s="22" t="str">
+      <c r="G9" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H9" s="22" t="str">
+      <c r="H9" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I9" s="22" t="str">
+      <c r="I9" t="str" s="22">
         <v>通常マド/テラス MW/MH、止水部材</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="str">
+      <c r="A10" t="str" s="22">
         <v>CM-EV-008</v>
       </c>
-      <c r="B10" s="22" t="str">
+      <c r="B10" t="str" s="22">
         <v>LIXIL公式納まり</v>
       </c>
-      <c r="C10" s="22" t="str">
+      <c r="C10" t="str" s="22">
         <v>リプラス 汎用カットモール シャッター納まり</v>
       </c>
-      <c r="D10" s="22" t="str">
+      <c r="D10" t="str" s="22">
         <v>2026現行</v>
       </c>
-      <c r="E10" s="22" t="str">
+      <c r="E10" t="str" s="22">
         <v>P190-191</v>
       </c>
-      <c r="F10" s="22" t="str">
+      <c r="F10" t="str" s="22">
         <v>Drive:1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT</v>
       </c>
-      <c r="G10" s="22" t="str">
+      <c r="G10" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H10" s="22" t="str">
+      <c r="H10" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I10" s="22" t="str">
+      <c r="I10" t="str" s="22">
         <v>シャッターMW/MH、シーリング</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="str">
+      <c r="A11" t="str" s="22">
         <v>CM-EV-009</v>
       </c>
-      <c r="B11" s="22" t="str">
+      <c r="B11" t="str" s="22">
         <v>LIXIL公式納まり</v>
       </c>
-      <c r="C11" s="22" t="str">
+      <c r="C11" t="str" s="22">
         <v>リプラス 汎用カットモール 雨戸付納まり</v>
       </c>
-      <c r="D11" s="22" t="str">
+      <c r="D11" t="str" s="22">
         <v>2026現行</v>
       </c>
-      <c r="E11" s="22" t="str">
+      <c r="E11" t="str" s="22">
         <v>業務用資料/納まり</v>
       </c>
-      <c r="F11" s="22" t="str">
+      <c r="F11" t="str" s="22">
         <v>Drive:1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr</v>
       </c>
-      <c r="G11" s="22" t="str">
+      <c r="G11" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H11" s="22" t="str">
+      <c r="H11" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I11" s="22" t="str">
+      <c r="I11" t="str" s="22">
         <v>雨戸付MW/MH</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="str">
+      <c r="A12" t="str" s="22">
         <v>CM-EV-010</v>
       </c>
-      <c r="B12" s="22" t="str">
+      <c r="B12" t="str" s="22">
         <v>LIXIL公式現調</v>
       </c>
-      <c r="C12" s="22" t="str">
+      <c r="C12" t="str" s="22">
         <v>リプラス 汎用カットモール 現場調査シート</v>
       </c>
-      <c r="D12" s="22" t="str">
+      <c r="D12" t="str" s="22">
         <v>2026現行</v>
       </c>
-      <c r="E12" s="22" t="str">
+      <c r="E12" t="str" s="22">
         <v>P276</v>
       </c>
-      <c r="F12" s="22" t="str">
+      <c r="F12" t="str" s="22">
         <v>Drive:1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT</v>
       </c>
-      <c r="G12" s="22" t="str">
+      <c r="G12" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H12" s="22" t="str">
+      <c r="H12" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I12" s="22" t="str">
+      <c r="I12" t="str" s="22">
         <v>TW公式モール寸法：引違いMADO MW=W+16/MH=H+41、引違いTERRACE MW=W+16/MH=H+81、装飾MADO MW=W+16/MH=H+28、装飾TERRACE/採風勝手口/テラスドア MW=W+16/MH=H+68。</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="str">
+      <c r="A13" t="str" s="22">
         <v>CM-EV-011</v>
       </c>
-      <c r="B13" s="22" t="str">
+      <c r="B13" t="str" s="22">
         <v>LIXIL公式現調</v>
       </c>
-      <c r="C13" s="22" t="str">
+      <c r="C13" t="str" s="22">
         <v>リプラス 現場調査マニュアル 汎用カットモール</v>
       </c>
-      <c r="D13" s="22" t="str">
+      <c r="D13" t="str" s="22">
         <v>2026現行</v>
       </c>
-      <c r="E13" s="22" t="str">
+      <c r="E13" t="str" s="22">
         <v>P273前後</v>
       </c>
-      <c r="F13" s="22" t="str">
+      <c r="F13" t="str" s="22">
         <v>Drive:1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT</v>
       </c>
-      <c r="G13" s="22" t="str">
+      <c r="G13" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H13" s="22" t="str">
+      <c r="H13" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I13" s="22" t="str">
+      <c r="I13" t="str" s="22">
         <v>木造、a/b/c、壁切断、土間、下地</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="str">
+      <c r="A14" t="str" s="22">
         <v>CM-EV-012</v>
       </c>
-      <c r="B14" s="22" t="str">
+      <c r="B14" t="str" s="22">
         <v>LIXIL公式現調</v>
       </c>
-      <c r="C14" s="22" t="str">
+      <c r="C14" t="str" s="22">
         <v>汎用カットモール 新設サッシ対応可否</v>
       </c>
-      <c r="D14" s="22" t="str">
+      <c r="D14" t="str" s="22">
         <v>2026現行</v>
       </c>
-      <c r="E14" s="22" t="str">
+      <c r="E14" t="str" s="22">
         <v>P273</v>
       </c>
-      <c r="F14" s="22" t="str">
+      <c r="F14" t="str" s="22">
         <v>Drive:1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT</v>
       </c>
-      <c r="G14" s="22" t="str">
+      <c r="G14" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H14" s="22" t="str">
+      <c r="H14" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I14" s="22" t="str">
+      <c r="I14" t="str" s="22">
         <v>外付不可/4シリーズ</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="str">
+      <c r="A15" t="str" s="22">
         <v>CM-EV-013</v>
       </c>
-      <c r="B15" s="22" t="str">
+      <c r="B15" t="str" s="22">
         <v>LIXIL公式現調</v>
       </c>
-      <c r="C15" s="22" t="str">
+      <c r="C15" t="str" s="22">
         <v>汎用カットモール 寸法変更・干渉条件</v>
       </c>
-      <c r="D15" s="22" t="str">
+      <c r="D15" t="str" s="22">
         <v>2026現行</v>
       </c>
-      <c r="E15" s="22" t="str">
+      <c r="E15" t="str" s="22">
         <v>現調注意</v>
       </c>
-      <c r="F15" s="22" t="str">
+      <c r="F15" t="str" s="22">
         <v>Drive:1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr</v>
       </c>
-      <c r="G15" s="22" t="str">
+      <c r="G15" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H15" s="22" t="str">
+      <c r="H15" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I15" s="22" t="str">
+      <c r="I15" t="str" s="22">
         <v>同寸基本、大きい=開口拡大、小さい不可、枠付面格子不可</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="str">
+      <c r="A16" t="str" s="22">
         <v>CM-EV-014</v>
       </c>
-      <c r="B16" s="22" t="str">
+      <c r="B16" t="str" s="22">
         <v>LIXIL公式価格/納まり</v>
       </c>
-      <c r="C16" s="22" t="str">
+      <c r="C16" t="str" s="22">
         <v>カットモール用窓枠・内装調整アングル</v>
       </c>
-      <c r="D16" s="22" t="str">
+      <c r="D16" t="str" s="22">
         <v>2026現行</v>
       </c>
-      <c r="E16" s="22" t="str">
+      <c r="E16" t="str" s="22">
         <v>P273/納まり</v>
       </c>
-      <c r="F16" s="22" t="str">
+      <c r="F16" t="str" s="22">
         <v>Drive:1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT</v>
       </c>
-      <c r="G16" s="22" t="str">
+      <c r="G16" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H16" s="22" t="str">
+      <c r="H16" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I16" s="22" t="str">
+      <c r="I16" t="str" s="22">
         <v>内装部材組合せ</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="str">
+      <c r="A17" t="str" s="22">
         <v>CM-EV-015</v>
       </c>
-      <c r="B17" s="22" t="str">
+      <c r="B17" t="str" s="22">
         <v>LIXIL公式カタログ</v>
       </c>
-      <c r="C17" s="22" t="str">
+      <c r="C17" t="str" s="22">
         <v>リプラス 商品カタログ｜汎用カットモール カラーバリエーション</v>
       </c>
-      <c r="D17" s="22" t="str">
+      <c r="D17" t="str" s="22">
         <v>2025-08/2026現行</v>
       </c>
-      <c r="E17" s="22" t="str">
+      <c r="E17" t="str" s="22">
         <v>P47</v>
       </c>
-      <c r="F17" s="22" t="str">
+      <c r="F17" t="str" s="22">
         <v>Drive:1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT</v>
       </c>
-      <c r="G17" s="22" t="str">
+      <c r="G17" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H17" s="22" t="str">
+      <c r="H17" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I17" s="22" t="str">
+      <c r="I17" t="str" s="22">
         <v>室外カットモール5色、カットモール用窓枠6色、新築用窓枠7色、内装調整アングル9色を公式掲載。</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="str">
+      <c r="A18" t="str" s="22">
         <v>CM-EV-016</v>
       </c>
-      <c r="B18" s="22" t="str">
+      <c r="B18" t="str" s="22">
         <v>成果物仕様</v>
       </c>
-      <c r="C18" s="22" t="str">
+      <c r="C18" t="str" s="22">
         <v>成果物パッケージ・保管・完了ゲート仕様書 v2.0</v>
       </c>
-      <c r="D18" s="22" t="str">
+      <c r="D18" t="str" s="22">
         <v>v2.0</v>
       </c>
-      <c r="E18" s="22" t="str">
+      <c r="E18" t="str" s="22">
         <v>Authoring+Runtime+Documentation/APG/SG</v>
       </c>
-      <c r="F18" s="22" t="str">
+      <c r="F18" t="str" s="22">
         <v>Drive:1onE_nzUJhj-w1VnvIS4IGW9YRAanpxm8Jp4WYkFrBFg</v>
       </c>
-      <c r="G18" s="22" t="str">
+      <c r="G18" t="str" s="22">
         <v>2026-09-01</v>
       </c>
-      <c r="H18" s="22" t="str">
+      <c r="H18" t="str" s="22">
         <v>HIGH</v>
       </c>
-      <c r="I18" s="22" t="str">
+      <c r="I18" t="str" s="22">
         <v>Package Gate/Storage Gate</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>DELTA-CUT-WOOD-EV-V4</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>PDF 122</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>UPDATE_CUT_MALL_WINDOW_FRAME_COLOR_ONLY / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A19" t="str" s="22">
+        <v>DELTA-CUT-WOOD-EV-V4</v>
+      </c>
+      <c r="B19" t="str" s="22">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C19" t="str" s="22">
+        <v>IS9800</v>
+      </c>
+      <c r="D19" t="str" s="22">
+        <v>2026-10</v>
+      </c>
+      <c r="E19" t="str" s="22">
+        <v>PDF 122</v>
+      </c>
+      <c r="F19" t="str" s="22">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G19" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H19" t="str" s="22">
+        <v>HIGH</v>
+      </c>
+      <c r="I19" t="str" s="22">
+        <v>UPDATE_CUT_MALL_WINDOW_FRAME_COLOR_ONLY / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>REF-TW-CURRENT-20261009-V4</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>Current正本参照</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>integrated-v0.5 Current Authoring</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>固定参照ID/SHA</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/10-ygy_wcdXN2u9brqU1AhucboJv5N5qk/view</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>5062503d3387999c2eed0862b3386e5248ae131008cbc37975956d709d598ba6</t>
-        </is>
+      <c r="A20" t="str" s="22">
+        <v>REF-TW-CURRENT-20261009-V4</v>
+      </c>
+      <c r="B20" t="str" s="22">
+        <v>Current正本参照</v>
+      </c>
+      <c r="C20" t="str" s="22">
+        <v>integrated-v0.5 Current Authoring</v>
+      </c>
+      <c r="D20" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="E20" t="str" s="22">
+        <v>固定参照ID/SHA</v>
+      </c>
+      <c r="F20" t="str" s="22">
+        <v>https://drive.google.com/file/d/10-ygy_wcdXN2u9brqU1AhucboJv5N5qk/view</v>
+      </c>
+      <c r="G20" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H20" t="str" s="22">
+        <v>HIGH</v>
+      </c>
+      <c r="I20" t="str" s="22">
+        <v>5062503d3387999c2eed0862b3386e5248ae131008cbc37975956d709d598ba6</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>REF-S2-CURRENT-20261009-V4</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>Current正本参照</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>v0.9-R4 Current Authoring</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>固定参照ID/SHA</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1_p-xJ9Mv7FecoR8Me0E43f3LEEkpVQSP/view</t>
-        </is>
-      </c>
-      <c r="G21" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>eeb285689a1e8a78469d5d13d1e015083d7f2e71ab274427dcfd413e33adc8e4</t>
-        </is>
+      <c r="A21" t="str" s="22">
+        <v>REF-S2-CURRENT-20261009-V4</v>
+      </c>
+      <c r="B21" t="str" s="22">
+        <v>Current正本参照</v>
+      </c>
+      <c r="C21" t="str" s="22">
+        <v>v0.9-R4 Current Authoring</v>
+      </c>
+      <c r="D21" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="E21" t="str" s="22">
+        <v>固定参照ID/SHA</v>
+      </c>
+      <c r="F21" t="str" s="22">
+        <v>https://drive.google.com/file/d/1_p-xJ9Mv7FecoR8Me0E43f3LEEkpVQSP/view</v>
+      </c>
+      <c r="G21" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H21" t="str" s="22">
+        <v>HIGH</v>
+      </c>
+      <c r="I21" t="str" s="22">
+        <v>eeb285689a1e8a78469d5d13d1e015083d7f2e71ab274427dcfd413e33adc8e4</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>REF-SL-CURRENT-20261009-V4</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>Current正本参照</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>v0.7-R3 Current Authoring</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>固定参照ID/SHA</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/19sjSAPwyd30fF5akazldGs0wkhOGZF9v/view</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>42a1a159c199ac0290f4862b20381abf2450b686ae8a8a2abdaa2d428a8c73f8</t>
-        </is>
+      <c r="A22" t="str" s="22">
+        <v>REF-SL-CURRENT-20261009-V4</v>
+      </c>
+      <c r="B22" t="str" s="22">
+        <v>Current正本参照</v>
+      </c>
+      <c r="C22" t="str" s="22">
+        <v>v0.7-R3 Current Authoring</v>
+      </c>
+      <c r="D22" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="E22" t="str" s="22">
+        <v>固定参照ID/SHA</v>
+      </c>
+      <c r="F22" t="str" s="22">
+        <v>https://drive.google.com/file/d/19sjSAPwyd30fF5akazldGs0wkhOGZF9v/view</v>
+      </c>
+      <c r="G22" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H22" t="str" s="22">
+        <v>HIGH</v>
+      </c>
+      <c r="I22" t="str" s="22">
+        <v>42a1a159c199ac0290f4862b20381abf2450b686ae8a8a2abdaa2d428a8c73f8</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>REF-A-CURRENT-20261009-V4</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>Current正本参照</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>v0.7 Current Authoring</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>固定参照ID/SHA</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1cDEFzi0g1DzM5YoeGvZtHuXionD7tmFD/view</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>1aae676ab404e9110ec6bb5aab522c6c0dc2fdc856a0d7c734fd2561fc5dfe47</t>
-        </is>
+      <c r="A23" t="str" s="22">
+        <v>REF-A-CURRENT-20261009-V4</v>
+      </c>
+      <c r="B23" t="str" s="22">
+        <v>Current正本参照</v>
+      </c>
+      <c r="C23" t="str" s="22">
+        <v>v0.7 Current Authoring</v>
+      </c>
+      <c r="D23" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="E23" t="str" s="22">
+        <v>固定参照ID/SHA</v>
+      </c>
+      <c r="F23" t="str" s="22">
+        <v>https://drive.google.com/file/d/1cDEFzi0g1DzM5YoeGvZtHuXionD7tmFD/view</v>
+      </c>
+      <c r="G23" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H23" t="str" s="22">
+        <v>HIGH</v>
+      </c>
+      <c r="I23" t="str" s="22">
+        <v>1aae676ab404e9110ec6bb5aab522c6c0dc2fdc856a0d7c734fd2561fc5dfe47</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>EV-V5-CUT-EXTERNAL</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>公式カタログ</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>SN1200</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>PDF277/280 印刷273/276</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>外付→外付新設、雨戸は鏡板付戸袋のみ、取付幅W+c。自動施工可にしない</t>
-        </is>
+      <c r="A24" t="str" s="22">
+        <v>EV-V5-CUT-EXTERNAL</v>
+      </c>
+      <c r="B24" t="str" s="22">
+        <v>公式カタログ</v>
+      </c>
+      <c r="C24" t="str" s="22">
+        <v>SN1200</v>
+      </c>
+      <c r="D24" t="str" s="22">
+        <v>2025-08</v>
+      </c>
+      <c r="E24" t="str" s="22">
+        <v>PDF277/280 印刷273/276</v>
+      </c>
+      <c r="F24" t="str" s="22">
+        <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
+      </c>
+      <c r="G24" t="str" s="22">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H24" t="str" s="22">
+        <v>HIGH</v>
+      </c>
+      <c r="I24" t="str" s="22">
+        <v>外付→外付新設、雨戸は鏡板付戸袋のみ、取付幅W+c。自動施工可にしない</v>
       </c>
     </row>
   </sheetData>
@@ -17286,7 +17178,7 @@
         <v>リプラス住宅用 → 仕様</v>
       </c>
       <c r="E4" t="str" s="22">
-        <v>今回承認されたアプリ運用ルール</v>
+        <v>アプリ運用ルール</v>
       </c>
       <c r="F4"/>
     </row>
@@ -17340,7 +17232,7 @@
         <v>選択・確認</v>
       </c>
       <c r="E7" t="str" s="22">
-        <v>本体色に連動</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F7"/>
     </row>
@@ -17358,7 +17250,7 @@
         <v>選択・確認</v>
       </c>
       <c r="E8" t="str" s="22">
-        <v>本体色に連動</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F8"/>
     </row>
@@ -17394,7 +17286,7 @@
         <v>選択・確認</v>
       </c>
       <c r="E10" t="str" s="22">
-        <v>採寸後に再評価</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F10"/>
     </row>

--- a/changes/replus-runtime-v5/candidates/RPL_CUT_MALL.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_CUT_MALL.xlsx
@@ -473,7 +473,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -531,7 +531,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -545,13 +545,13 @@
         <v>new_sash_exterior_color</v>
       </c>
       <c r="D7" t="str" s="22">
-        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E7" t="str" s="22">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -569,7 +569,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -583,13 +583,13 @@
         <v>new_sash_interior_color</v>
       </c>
       <c r="D9" t="str" s="22">
-        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E9" t="str" s="22">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -607,7 +607,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -625,7 +625,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -643,7 +643,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -661,7 +661,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -681,7 +681,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -701,7 +701,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -719,7 +719,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -737,7 +737,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="18">
